--- a/137554_Cuenca_Rimac/_raw_reportes_xlsx/IDConfig_67731_completo.xlsx
+++ b/137554_Cuenca_Rimac/_raw_reportes_xlsx/IDConfig_67731_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Rd76b6d4644004711"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Rb4079f3529174584"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -174,7 +174,7 @@
       </x:c>
       <x:c s="" t="inlineStr">
         <x:is>
-          <x:t>Dpto: Lima / Prov: Huarochiri / Dist.: San Mateo</x:t>
+          <x:t>Dpto: Lima / Prov: Huarochirí / Dist.: San Mateo</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -250,6 +250,141 @@
         <x:is>
           <x:t>VALOR (m³/s)</x:t>
         </x:is>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.6814</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.8679</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.8679</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.6137</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.6137</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.6814</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.9866</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.8001</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.5292</x:v>
       </x:c>
     </x:row>
     <x:row>

--- a/137554_Cuenca_Rimac/_raw_reportes_xlsx/IDConfig_67731_completo.xlsx
+++ b/137554_Cuenca_Rimac/_raw_reportes_xlsx/IDConfig_67731_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Rb4079f3529174584"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R419fe216927e4bac"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,726 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>10/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.4272</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.1731</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.1731</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.5460</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.9866</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.5460</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.7834</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.1731</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.6137</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.4272</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.4272</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.4272</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.9866</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.2918</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.4272</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.8001</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.8002</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.6137</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.6137</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.6137</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.4272</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.1731</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.9699</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.5970</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.4782</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.6814</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.0543</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.8001</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.8001</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.4105</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.7324</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.3595</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.7324</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.1053</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.9189</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.8512</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.2918</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.8002</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.4272</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.1731</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.8002</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.9866</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.4272</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.0543</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.5460</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.8512</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.8512</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.2408</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>23/08/2026</x:t>
         </x:is>
       </x:c>
@@ -369,7 +1089,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      5.8001</x:v>
+        <x:v>      5.8002</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -384,7 +1104,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      9.5292</x:v>
+        <x:v>      9.5293</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -474,7 +1194,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      9.5292</x:v>
+        <x:v>      9.5293</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -504,7 +1224,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      5.8001</x:v>
+        <x:v>      5.8002</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1104,7 +1824,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      9.5292</x:v>
+        <x:v>      9.5293</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -20206,6 +20926,3276 @@
       <x:c s="1" t="inlineStr">
         <x:is>
           <x:t>01/01/2023</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     11.0209</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/12/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     11.3938</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/12/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.9699</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/12/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.1563</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/12/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.4105</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/12/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     10.2751</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/12/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.9022</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/12/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.2241</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/12/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     10.2751</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/12/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     10.2751</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/12/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.3428</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/12/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.5460</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/12/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.4782</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/12/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.5970</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/12/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.5293</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/12/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.5970</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/12/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.9022</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/12/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     11.0209</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/12/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     10.0886</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/12/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.9699</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/12/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.5460</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/12/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.2408</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/12/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.8002</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/12/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.7834</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/12/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.8512</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/12/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.5460</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/12/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.2408</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/12/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.3595</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/12/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.6137</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/12/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.2408</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/12/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.6137</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/12/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.4272</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/11/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.9866</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/11/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.9866</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/11/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.8002</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/11/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.9866</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/11/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.9866</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/11/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.3595</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/11/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.6137</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/11/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.4272</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/11/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.6137</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/11/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.6137</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/11/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.6137</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/11/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.8679</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/11/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.2408</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/11/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.0543</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/11/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.4272</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/11/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.2408</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/11/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.2408</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/11/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.1731</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/11/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.4272</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/11/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.9866</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/11/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.8679</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/11/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.8002</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/11/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.6137</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/11/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.6137</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/11/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.6137</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/11/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.9866</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/11/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.8002</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/11/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.9866</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/11/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.1731</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/11/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.1731</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/10/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.8002</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/10/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.6137</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/10/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.4272</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/10/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.6137</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/10/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.2408</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/10/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.8679</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/10/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.6137</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/10/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.6137</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/10/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.0543</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/10/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.2408</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/10/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.6137</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/10/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.8002</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/10/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.9866</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/10/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.8002</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/10/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.8002</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/10/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.6137</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/10/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.4272</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/10/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.6137</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/10/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.1731</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/10/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.8002</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/10/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.2408</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/10/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.4272</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/10/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.2408</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.3595</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.1731</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.0543</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.4272</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.9866</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.1053</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.5460</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.2918</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.4782</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.7324</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.9189</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.6647</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.5293</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.3085</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.4950</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.6647</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     11.0209</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.6647</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.9189</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.9189</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.2918</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.4782</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.2918</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.6647</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.1053</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.1053</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.9189</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.9189</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.9189</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.4782</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.7324</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.0376</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.1053</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.9189</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.4782</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.1053</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.4782</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.5970</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.4782</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.6647</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.4105</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.9699</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.0376</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.4105</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.9699</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.0376</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/08/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.8512</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.9699</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.2241</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.9699</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.7834</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.1563</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.5970</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.4105</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.5970</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/08/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.5293</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/08/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.9699</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/08/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.7834</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/08/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.9699</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/08/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.3428</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/08/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.1563</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/08/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.0376</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/08/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.9699</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/08/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.5293</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/08/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.9699</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/08/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.1563</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/08/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.5970</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/08/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.4105</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/08/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.7834</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/07/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.7834</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/07/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.7834</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/07/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.3428</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/07/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.4105</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/07/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.7834</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/07/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.1563</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/07/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.5293</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/07/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.1563</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/07/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.5970</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/07/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.1563</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/07/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.4105</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/07/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.7834</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/07/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.7834</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/07/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.3428</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/07/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     10.8344</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/07/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     11.3938</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/07/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     11.3938</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/07/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.5970</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/07/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.4105</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/07/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.7834</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/07/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.9699</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/07/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.1563</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/07/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.0376</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/07/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.4105</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/07/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.9699</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/07/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.5970</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/07/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.9699</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/07/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.9699</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/07/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.7834</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/07/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.3428</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/07/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.5293</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/06/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.5293</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/06/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.7500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/06/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.1906</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/06/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     14.0042</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/06/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     12.6990</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/06/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     12.1396</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/06/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.1563</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/06/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.5293</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/06/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     10.0886</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/06/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.5293</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/06/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.4105</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/06/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.1563</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/06/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.9022</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/06/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.9022</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/06/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     10.6480</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/06/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     11.5803</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/06/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     10.6480</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/06/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     10.8344</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/06/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     11.7667</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/06/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.5293</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/06/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.8512</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/06/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.2241</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/06/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.9699</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/06/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.9022</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/06/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.7834</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/06/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.2241</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/06/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.9699</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/06/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.1563</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/06/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.9699</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/06/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.3428</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/05/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     10.2751</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/05/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     11.0209</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/05/2022</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     11.2073</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/05/2022</x:t>
         </x:is>
       </x:c>
       <x:c s="7" t="inlineStr">
